--- a/FPA_Financial_Model.xlsx
+++ b/FPA_Financial_Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agamp\Desktop\FP&amp;A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agamp\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{C06D5F4C-2805-4D30-86A7-5098659F7CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA61F69-1F3A-473B-83C3-C91150CF18EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Debt Schedule" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
   <si>
     <t>Financial Statements</t>
   </si>
@@ -47,9 +46,6 @@
     <t>Income Statement</t>
   </si>
   <si>
-    <t>Figures in USD millions</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -83,9 +79,6 @@
     <t>Balance Sheet</t>
   </si>
   <si>
-    <t>Figures in USD</t>
-  </si>
-  <si>
     <t>Cash &amp; Cash Equivalents</t>
   </si>
   <si>
@@ -372,6 +365,9 @@
   </si>
   <si>
     <t>CALCULATIONS FOR SENSTIVITY ANALYSIS</t>
+  </si>
+  <si>
+    <t>Figures in INR</t>
   </si>
 </sst>
 </file>
@@ -384,7 +380,7 @@
     <numFmt numFmtId="166" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="\₹#,##0"/>
+    <numFmt numFmtId="169" formatCode="\₹#,##0"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1070,6 +1066,81 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1077,6 +1148,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1086,82 +1169,16 @@
     <xf numFmtId="0" fontId="10" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="16" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1169,27 +1186,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1222,9 +1218,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>182384</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2935</xdr:rowOff>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1059180</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1248,8 +1244,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5954692" y="168398"/>
-          <a:ext cx="583959" cy="588917"/>
+          <a:off x="7459098" y="168398"/>
+          <a:ext cx="953382" cy="890782"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1600,7 +1596,7 @@
     <col min="15" max="15" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.2" customHeight="1">
+    <row r="1" spans="1:10" ht="96.6" customHeight="1">
       <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1625,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="7">
@@ -1655,7 +1651,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10">
@@ -1681,7 +1677,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10">
@@ -1707,7 +1703,7 @@
     </row>
     <row r="7" spans="1:10" ht="31.2" customHeight="1">
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11">
@@ -1734,7 +1730,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10">
@@ -1760,7 +1756,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="10">
@@ -1786,7 +1782,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="10">
@@ -1812,7 +1808,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11">
@@ -1838,7 +1834,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11">
@@ -1864,7 +1860,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10">
@@ -1890,7 +1886,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12">
@@ -1919,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1930,7 +1926,7 @@
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C17" s="6">
         <v>2025</v>
@@ -1958,7 +1954,7 @@
     </row>
     <row r="18" spans="2:10">
       <c r="B18" s="33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" s="34">
         <v>14589</v>
@@ -1984,12 +1980,12 @@
         <v>91753.804550442699</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C19" s="13">
         <v>9877</v>
@@ -2017,7 +2013,7 @@
     </row>
     <row r="20" spans="2:10">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" s="13">
         <v>8579</v>
@@ -2045,7 +2041,7 @@
     </row>
     <row r="21" spans="2:10">
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" s="11">
         <f t="shared" ref="C21:H21" si="0">SUM(C18:C20)</f>
@@ -2074,7 +2070,7 @@
     </row>
     <row r="22" spans="2:10">
       <c r="B22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22" s="13">
         <v>48990</v>
@@ -2100,12 +2096,12 @@
         <v>58945</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C23" s="12">
         <f t="shared" ref="C23:H23" si="1">SUM(C21,C22)</f>
@@ -2134,7 +2130,7 @@
     </row>
     <row r="25" spans="2:10">
       <c r="B25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25" s="13">
         <v>14880</v>
@@ -2162,7 +2158,7 @@
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C26" s="35">
         <v>0</v>
@@ -2188,13 +2184,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J26" s="36"/>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27" s="11">
         <f t="shared" ref="C27:H27" si="2">SUM(C25,C26)</f>
@@ -2223,7 +2219,7 @@
     </row>
     <row r="29" spans="2:10">
       <c r="B29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29" s="13">
         <v>40000</v>
@@ -2251,7 +2247,7 @@
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C30" s="14">
         <f t="shared" ref="C30:H30" si="3">SUM(C27,C29)</f>
@@ -2280,7 +2276,7 @@
     </row>
     <row r="32" spans="2:10">
       <c r="B32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C32" s="13">
         <v>25000</v>
@@ -2300,14 +2296,14 @@
       <c r="H32" s="10">
         <v>25000</v>
       </c>
-      <c r="I32" s="81" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="81"/>
+      <c r="I32" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="70"/>
     </row>
     <row r="33" spans="1:9">
       <c r="B33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="13">
         <f>24155-22000</f>
@@ -2334,12 +2330,12 @@
         <v>93279.298075000013</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="B34" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="14">
         <f t="shared" ref="C34:H34" si="4">SUM(C32:C33)</f>
@@ -2368,7 +2364,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C36" s="12">
         <f t="shared" ref="C36:H36" si="5">SUM(C30,C34)</f>
@@ -2397,7 +2393,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="B38" s="23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C38" s="24">
         <f t="shared" ref="C38:H38" si="6">C23-C36</f>
@@ -2429,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -2440,7 +2436,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" s="10">
         <f>D14</f>
@@ -2466,7 +2462,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="10">
         <f>D100</f>
@@ -2491,7 +2487,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="B43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" ref="D43:H44" si="7">-D19+C19</f>
@@ -2516,7 +2512,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="B44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="7"/>
@@ -2541,7 +2537,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="B45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D45" s="10">
         <f>D25-C25</f>
@@ -2566,7 +2562,7 @@
     </row>
     <row r="46" spans="1:9">
       <c r="B46" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="14">
@@ -2592,7 +2588,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="B48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D48" s="10">
         <f>-D85</f>
@@ -2617,7 +2613,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="B49" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="14">
@@ -2643,7 +2639,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="B51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D51" s="10">
         <f>D79-E79</f>
@@ -2668,7 +2664,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="B52" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
@@ -2678,7 +2674,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="B53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D53" s="10">
         <f>D32-C32</f>
@@ -2703,7 +2699,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="B54" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D54" s="10">
         <f>D110</f>
@@ -2728,7 +2724,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="B55" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="14">
@@ -2754,7 +2750,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="B57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D57" s="10">
         <f>C18</f>
@@ -2779,7 +2775,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="B58" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="12">
@@ -2805,7 +2801,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="B59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D59" s="10">
         <f>D57+D58</f>
@@ -2842,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -2853,7 +2849,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="B62" s="26" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="9">
         <v>2025</v>
@@ -2876,7 +2872,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="B63" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C63" s="21"/>
       <c r="D63" s="21">
@@ -2897,7 +2893,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="B64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C64" s="21"/>
       <c r="D64" s="21">
@@ -2918,7 +2914,7 @@
     </row>
     <row r="66" spans="2:10">
       <c r="B66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="19">
@@ -2939,7 +2935,7 @@
     </row>
     <row r="67" spans="2:10">
       <c r="B67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="19">
@@ -2968,7 +2964,7 @@
     </row>
     <row r="69" spans="2:10">
       <c r="B69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="18"/>
       <c r="D69" s="18">
@@ -2989,7 +2985,7 @@
     </row>
     <row r="71" spans="2:10">
       <c r="B71" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" s="13">
         <v>158997</v>
@@ -3002,7 +2998,7 @@
     </row>
     <row r="72" spans="2:10">
       <c r="B72" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C72" s="13">
         <v>75889</v>
@@ -3015,7 +3011,7 @@
     </row>
     <row r="74" spans="2:10">
       <c r="B74" s="26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
@@ -3051,7 +3047,7 @@
         <v>6.2120668943439185E-2</v>
       </c>
       <c r="J75" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="2:10">
@@ -3081,7 +3077,7 @@
         <v>0.11304668660807232</v>
       </c>
       <c r="J76" s="31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="2:10">
@@ -3111,12 +3107,12 @@
         <v>0.1960758476195496</v>
       </c>
       <c r="J77" s="31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="2:10">
       <c r="B79" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13">
@@ -3141,7 +3137,7 @@
     </row>
     <row r="80" spans="2:10">
       <c r="B80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="19">
@@ -3162,7 +3158,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="B81" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10">
@@ -3200,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -3211,7 +3207,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="B84" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
@@ -3222,7 +3218,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="B85" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D85" s="13">
         <v>15000</v>
@@ -3242,7 +3238,7 @@
     </row>
     <row r="87" spans="1:10">
       <c r="B87" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C87" s="15">
         <v>10</v>
@@ -3250,7 +3246,7 @@
     </row>
     <row r="88" spans="1:10">
       <c r="B88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C88" s="15">
         <v>10</v>
@@ -3258,7 +3254,7 @@
     </row>
     <row r="89" spans="1:10">
       <c r="B89" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C89" s="10">
         <f>C22</f>
@@ -3287,7 +3283,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="C91" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D91" s="1">
         <v>2026</v>
@@ -3305,7 +3301,7 @@
         <v>2030</v>
       </c>
       <c r="J91" s="31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3334,7 +3330,7 @@
         <v>1500</v>
       </c>
       <c r="J92" s="31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3359,7 +3355,7 @@
         <v>1200</v>
       </c>
       <c r="J93" s="31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3412,7 +3408,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="B98" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D98" s="10">
         <f>C89/C88</f>
@@ -3437,7 +3433,7 @@
     </row>
     <row r="99" spans="1:10">
       <c r="B99" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D99" s="10">
         <f>SUM(D92:D96)</f>
@@ -3462,7 +3458,7 @@
     </row>
     <row r="100" spans="1:10">
       <c r="B100" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="14">
@@ -3488,7 +3484,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="B102" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D102" s="10">
         <f>C22</f>
@@ -3511,12 +3507,12 @@
         <v>61544</v>
       </c>
       <c r="J102" s="31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="B103" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D103" s="10">
         <f>D85</f>
@@ -3541,7 +3537,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="B104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D104" s="10">
         <f>-D100</f>
@@ -3566,7 +3562,7 @@
     </row>
     <row r="105" spans="1:10">
       <c r="B105" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="11">
@@ -3595,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
@@ -3606,7 +3602,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="B108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="10">
@@ -3632,7 +3628,7 @@
     </row>
     <row r="109" spans="1:10">
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="10">
@@ -3658,7 +3654,7 @@
     </row>
     <row r="110" spans="1:10">
       <c r="B110" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="13">
@@ -3679,7 +3675,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="B111" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14">
@@ -3708,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -3719,7 +3715,7 @@
     </row>
     <row r="114" spans="1:9">
       <c r="B114" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
@@ -3730,7 +3726,7 @@
     </row>
     <row r="115" spans="1:9">
       <c r="B115" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D115" s="10">
         <f>C18</f>
@@ -3755,7 +3751,7 @@
     </row>
     <row r="116" spans="1:9">
       <c r="B116" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D116" s="10">
         <f>D46</f>
@@ -3780,7 +3776,7 @@
     </row>
     <row r="117" spans="1:9">
       <c r="B117" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D117" s="10">
         <f>D49</f>
@@ -3805,7 +3801,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="B118" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D118" s="10">
         <f>0</f>
@@ -3830,7 +3826,7 @@
     </row>
     <row r="119" spans="1:9">
       <c r="B119" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D119" s="10">
         <f>0</f>
@@ -3855,7 +3851,7 @@
     </row>
     <row r="120" spans="1:9">
       <c r="B120" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D120" s="10">
         <f>D110</f>
@@ -3880,7 +3876,7 @@
     </row>
     <row r="121" spans="1:9">
       <c r="B121" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C121" s="8"/>
       <c r="D121" s="14">
@@ -3906,7 +3902,7 @@
     </row>
     <row r="123" spans="1:9">
       <c r="B123" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
@@ -3917,7 +3913,7 @@
     </row>
     <row r="124" spans="1:9">
       <c r="B124" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D124" s="10">
         <f>C26</f>
@@ -3942,7 +3938,7 @@
     </row>
     <row r="125" spans="1:9">
       <c r="B125" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D125" s="10">
         <f>IF(D121&lt;0,-D121,-MIN(D124,D121))</f>
@@ -3968,7 +3964,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="B126" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C126" s="14"/>
       <c r="D126" s="14">
@@ -3994,7 +3990,7 @@
     </row>
     <row r="128" spans="1:9">
       <c r="B128" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D128" s="18">
         <v>0.05</v>
@@ -4014,7 +4010,7 @@
     </row>
     <row r="129" spans="1:8">
       <c r="B129" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D129" s="10">
         <f>D124*D128</f>
@@ -4042,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C130" s="14"/>
       <c r="D130" s="14">
@@ -4072,25 +4068,25 @@
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="C132" s="80" t="s">
-        <v>111</v>
-      </c>
-      <c r="D132" s="80"/>
-      <c r="E132" s="80"/>
-      <c r="F132" s="80"/>
+      <c r="C132" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="D132" s="69"/>
+      <c r="E132" s="69"/>
+      <c r="F132" s="69"/>
     </row>
     <row r="133" spans="1:8">
       <c r="B133" s="39"/>
       <c r="C133" s="1"/>
-      <c r="D133" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="E133" s="42"/>
-      <c r="F133" s="42"/>
+      <c r="D133" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="E133" s="67"/>
+      <c r="F133" s="67"/>
     </row>
     <row r="134" spans="1:8">
       <c r="B134" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C134" s="38">
         <f>H14</f>
@@ -4107,8 +4103,8 @@
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="B135" s="43" t="s">
-        <v>54</v>
+      <c r="B135" s="68" t="s">
+        <v>52</v>
       </c>
       <c r="C135">
         <v>490</v>
@@ -4125,7 +4121,7 @@
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="B136" s="42"/>
+      <c r="B136" s="67"/>
       <c r="C136">
         <v>500</v>
       </c>
@@ -4140,7 +4136,7 @@
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="B137" s="42"/>
+      <c r="B137" s="67"/>
       <c r="C137">
         <v>510</v>
       </c>
@@ -4229,94 +4225,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" thickBot="1">
-      <c r="A1" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="A1" s="71" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
     </row>
     <row r="2" spans="1:5" ht="22.05" customHeight="1" thickTop="1"/>
     <row r="3" spans="1:5" ht="27" customHeight="1">
-      <c r="A3" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="66">
+      <c r="A3" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="56">
         <f>statements!H14</f>
         <v>42702.857499999998</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="22.05" customHeight="1"/>
     <row r="5" spans="1:5" ht="28.05" customHeight="1">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48" t="s">
+      <c r="D5" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="48" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" thickBot="1">
+      <c r="A6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="49" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" thickBot="1">
-      <c r="A6" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="53">
+      <c r="B6" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="47">
         <f>statements!D135</f>
         <v>43564.818600000021</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="48">
         <f>statements!E135</f>
         <v>41644.996149999999</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="49">
         <f>statements!F135</f>
         <v>39725.173700000021</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1">
-      <c r="A7" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="56">
+      <c r="A7" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="74"/>
+      <c r="C7" s="50">
         <f xml:space="preserve"> statements!D136</f>
         <v>44661.86</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="51">
         <f>statements!E136</f>
         <v>42702.857499999998</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="52">
         <f>statements!F136</f>
         <v>40743.854999999996</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
-      <c r="A8" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="59">
+      <c r="A8" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="75"/>
+      <c r="C8" s="53">
         <f>statements!D137</f>
         <v>45758.901399999988</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="54">
         <f>statements!E137</f>
         <v>43760.718850000012</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="55">
         <f>statements!F137</f>
         <v>41762.536299999992</v>
       </c>
@@ -4341,238 +4337,238 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="73" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="A1" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
     </row>
     <row r="3" spans="1:7" ht="27" customHeight="1">
-      <c r="A3" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="67">
+      <c r="A3" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="57">
         <v>2025</v>
       </c>
-      <c r="C3" s="67">
+      <c r="C3" s="57">
         <v>2026</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="57">
         <v>2027</v>
       </c>
-      <c r="E3" s="67">
+      <c r="E3" s="57">
         <v>2028</v>
       </c>
-      <c r="F3" s="67">
+      <c r="F3" s="57">
         <v>2029</v>
       </c>
-      <c r="G3" s="67">
+      <c r="G3" s="57">
         <v>2030</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27" customHeight="1">
-      <c r="A4" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="68">
+      <c r="A4" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="58">
         <f>statements!C29</f>
         <v>40000</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="58">
         <f>B7</f>
         <v>40000</v>
       </c>
-      <c r="D4" s="68">
+      <c r="D4" s="58">
         <f>C7</f>
         <v>40000</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="58">
         <f>D7</f>
         <v>40000</v>
       </c>
-      <c r="F4" s="68">
+      <c r="F4" s="58">
         <f>E7</f>
         <v>40000</v>
       </c>
-      <c r="G4" s="68">
+      <c r="G4" s="58">
         <f>F7</f>
         <v>40000</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="69">
-        <v>0</v>
-      </c>
-      <c r="C5" s="69">
-        <v>0</v>
-      </c>
-      <c r="D5" s="69">
-        <v>0</v>
-      </c>
-      <c r="E5" s="69">
-        <v>0</v>
-      </c>
-      <c r="F5" s="69">
-        <v>0</v>
-      </c>
-      <c r="G5" s="69">
+      <c r="A5" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="59">
+        <v>0</v>
+      </c>
+      <c r="C5" s="59">
+        <v>0</v>
+      </c>
+      <c r="D5" s="59">
+        <v>0</v>
+      </c>
+      <c r="E5" s="59">
+        <v>0</v>
+      </c>
+      <c r="F5" s="59">
+        <v>0</v>
+      </c>
+      <c r="G5" s="59">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" customHeight="1" thickBot="1">
-      <c r="A6" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="70">
-        <v>0</v>
-      </c>
-      <c r="C6" s="70">
-        <v>0</v>
-      </c>
-      <c r="D6" s="70">
-        <v>0</v>
-      </c>
-      <c r="E6" s="70">
-        <v>0</v>
-      </c>
-      <c r="F6" s="70">
-        <v>0</v>
-      </c>
-      <c r="G6" s="70">
+      <c r="A6" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="60">
+        <v>0</v>
+      </c>
+      <c r="C6" s="60">
+        <v>0</v>
+      </c>
+      <c r="D6" s="60">
+        <v>0</v>
+      </c>
+      <c r="E6" s="60">
+        <v>0</v>
+      </c>
+      <c r="F6" s="60">
+        <v>0</v>
+      </c>
+      <c r="G6" s="60">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27" customHeight="1" thickBot="1">
-      <c r="A7" s="76" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="71">
+      <c r="A7" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="61">
         <f t="shared" ref="B7:G7" si="0">B4+B5-B6</f>
         <v>40000</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="61">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="61">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="E7" s="71">
+      <c r="E7" s="61">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="F7" s="71">
+      <c r="F7" s="61">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="G7" s="71">
+      <c r="G7" s="61">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16.2" thickTop="1"/>
     <row r="9" spans="1:7" ht="28.95" customHeight="1">
-      <c r="A9" s="77" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
+      <c r="A9" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
     </row>
     <row r="11" spans="1:7" ht="27" customHeight="1">
-      <c r="A11" s="75" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="68">
+      <c r="A11" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="58">
         <f t="shared" ref="B11:G11" si="1">B4</f>
         <v>40000</v>
       </c>
-      <c r="C11" s="68">
+      <c r="C11" s="58">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="D11" s="68">
+      <c r="D11" s="58">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="E11" s="68">
+      <c r="E11" s="58">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="F11" s="68">
+      <c r="F11" s="58">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
-      <c r="G11" s="68">
+      <c r="G11" s="58">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27" customHeight="1" thickBot="1">
-      <c r="A12" s="75" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="72">
+      <c r="A12" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G12" s="72">
+      <c r="G12" s="62">
         <f>statements!D80</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27" customHeight="1" thickBot="1">
-      <c r="A13" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="71">
+      <c r="A13" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="61">
         <f t="shared" ref="B13:G13" si="2">B11*B12</f>
         <v>2800.0000000000005</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13" s="61">
         <f t="shared" si="2"/>
         <v>2800.0000000000005</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D13" s="61">
         <f t="shared" si="2"/>
         <v>2800.0000000000005</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="61">
         <f t="shared" si="2"/>
         <v>2800.0000000000005</v>
       </c>
-      <c r="F13" s="71">
+      <c r="F13" s="61">
         <f t="shared" si="2"/>
         <v>2800.0000000000005</v>
       </c>
-      <c r="G13" s="71">
+      <c r="G13" s="61">
         <f t="shared" si="2"/>
         <v>2800.0000000000005</v>
       </c>

--- a/FPA_Financial_Model.xlsx
+++ b/FPA_Financial_Model.xlsx
@@ -1557,7 +1557,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
